--- a/data/summary_table_by_sheet.xlsx
+++ b/data/summary_table_by_sheet.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14914\Desktop\MESAM_Streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C67037-F239-4262-892A-0883458804C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C367AAB-4EFA-4473-B98A-68B45871688D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="22">
   <si>
     <t>muni_name</t>
   </si>
@@ -77,6 +91,15 @@
   </si>
   <si>
     <t>Wohlen (AG)</t>
+  </si>
+  <si>
+    <t>municipality</t>
+  </si>
+  <si>
+    <t>GPV (MW)</t>
+  </si>
+  <si>
+    <t>WT (MW)</t>
   </si>
 </sst>
 </file>
@@ -825,4 +848,161 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1460D41-4544-4A0E-B0A0-2DCE84D9CB3C}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="20.86328125" customWidth="1"/>
+    <col min="2" max="2" width="19.9296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2.57</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>22.39</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>8.25</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>477.95</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>